--- a/docs/downloads/04/tbl_homeland_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_homeland_marovoay_tous.xlsx
@@ -397,12 +397,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -420,12 +414,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -466,12 +454,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -489,12 +471,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -535,12 +511,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>5.7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -558,12 +528,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>5.7</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -604,12 +568,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>7.7</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -696,12 +654,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -742,12 +694,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D17">
-        <v>4</v>
-      </c>
-      <c r="E17">
-        <v>8.5</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -811,12 +757,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -856,12 +796,6 @@
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>11.8</v>
       </c>
     </row>
     <row r="23">

--- a/docs/downloads/04/tbl_homeland_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_homeland_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -418,7 +418,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -532,7 +532,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">

--- a/docs/downloads/04/tbl_homeland_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_homeland_marovoay_tous.xlsx
@@ -394,7 +394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -411,7 +411,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -428,7 +428,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D4">
@@ -451,7 +451,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D7">
@@ -508,7 +508,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D10">
@@ -565,8 +565,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
+          <t>Dans la commune</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>38.5</v>
       </c>
     </row>
     <row r="12">
@@ -582,14 +588,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>38.5</v>
+          <t>Dans le fokontany</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -605,7 +605,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D13">
@@ -628,14 +628,8 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>6</v>
-      </c>
-      <c r="E14">
-        <v>10.9</v>
+          <t>Dans la commune</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -651,8 +645,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
+          <t>Dans le fokontany</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>10.9</v>
       </c>
     </row>
     <row r="16">
@@ -668,7 +668,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D16">
@@ -691,8 +691,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
+          <t>Dans la commune</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>14.9</v>
       </c>
     </row>
     <row r="18">
@@ -708,14 +714,8 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>7</v>
-      </c>
-      <c r="E18">
-        <v>14.9</v>
+          <t>Dans le fokontany</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -731,7 +731,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D19">
@@ -754,7 +754,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D21">
@@ -794,7 +794,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D23">
@@ -834,14 +834,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="25">
@@ -857,14 +857,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="26">
@@ -880,7 +880,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D26">
@@ -903,14 +903,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E27">
-        <v>6.4</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="28">
@@ -926,14 +926,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
       <c r="D28">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>19.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="29">
@@ -949,7 +949,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D29">
